--- a/QCM3_1_PHY.xlsx
+++ b/QCM3_1_PHY.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VER_19JUIN_ASTUCES\DERNIERE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C446BAAF-B2D0-4D64-8D16-9933BB3F580C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A55D61-9A5A-43E1-92F0-0B1F174F7FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -892,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -942,232 +942,209 @@
       <c r="A2" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="14" t="s">
+      <c r="C3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="F5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B6" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14" t="s">
+      <c r="H6" s="14"/>
+      <c r="I6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="10" t="s">
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C7" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="C8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14" t="s">
+      <c r="H8" s="14"/>
+      <c r="I8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -1175,26 +1152,26 @@
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -1202,119 +1179,119 @@
     <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="14" t="s">
-        <v>105</v>
+      <c r="B12" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>109</v>
+        <v>49</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="14" t="s">
-        <v>107</v>
+      <c r="I12" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="102" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="102" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B14" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="14" t="s">
+      <c r="C14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F14" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14" t="s">
+      <c r="H14" s="14"/>
+      <c r="I14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J14" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14" t="s">
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>3</v>
@@ -1341,181 +1318,208 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="10" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B20" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="14" t="s">
+      <c r="C20" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E20" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F20" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G20" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="J20" s="19" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>80</v>
+      </c>
       <c r="H22" s="10"/>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="11"/>
+      <c r="B23" s="9"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM3_1_PHY.xlsx
+++ b/QCM3_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A55D61-9A5A-43E1-92F0-0B1F174F7FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BA97F2-D993-4CFF-BB0D-89191A17386D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
   <si>
     <t>Question</t>
   </si>
@@ -268,9 +268,6 @@
   </si>
   <si>
     <t>$50 \cdot 10^{-4}\text{ J}$</t>
-  </si>
-  <si>
-    <t>Le circuit de la figure ci-contre comprend quatre condensateurs dont les capacités sont identiques. La capacité $C_{AB}$ du condensateur équivalent est :</t>
   </si>
   <si>
     <t>Le circuit de la figure ci-dessous comprend quatre condensateurs et quatre conducteurs ohmiques : La résistance et la capacité équivalente :</t>
@@ -367,9 +364,6 @@
     <t>$U_R \cdot I \cdot \Delta t$</t>
   </si>
   <si>
-    <t>PHY_QCM1_3_Q1.png</t>
-  </si>
-  <si>
     <t>PHY_QCM1_3_Q2.png</t>
   </si>
   <si>
@@ -389,6 +383,10 @@
   </si>
   <si>
     <t>PHY_QCM1_3_Q9.png; PHY_QCM1_3_Q10.png</t>
+  </si>
+  <si>
+    <t>Le circuit de la figure ci-contre comprend quatre condensateurs dont les capacités sont identiques. &lt;br&gt;&lt;img src="/images/PHY_QCM1_3_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;La capacité $C_{AB}$ du condensateur équivalent est :</t>
   </si>
 </sst>
 </file>
@@ -892,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -940,40 +938,63 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
+    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>110</v>
+      <c r="C3" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
         <v>82</v>
@@ -982,147 +1003,145 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="B7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>114</v>
-      </c>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
+      <c r="B8" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>115</v>
-      </c>
+      <c r="C8" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
         <v>87</v>
@@ -1131,20 +1150,20 @@
         <v>3</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -1158,20 +1177,20 @@
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -1185,112 +1204,112 @@
         <v>3</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="10" t="s">
-        <v>90</v>
+      <c r="B12" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>52</v>
+        <v>107</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="10" t="s">
-        <v>50</v>
+      <c r="I12" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+    <row r="13" spans="1:11" ht="102" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>99</v>
+      </c>
       <c r="B13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="10"/>
+        <v>56</v>
+      </c>
+      <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="102" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>100</v>
-      </c>
+    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>116</v>
-      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -1318,31 +1337,31 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="10" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="10" t="s">
         <v>91</v>
@@ -1351,25 +1370,23 @@
         <v>3</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="I17" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="10" t="s">
         <v>92</v>
@@ -1378,78 +1395,78 @@
         <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="14" t="s">
+      <c r="C19" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="10" t="s">
         <v>95</v>
@@ -1458,68 +1475,43 @@
         <v>3</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>80</v>
-      </c>
+    </row>
+    <row r="22" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
       <c r="H22" s="10"/>
-      <c r="I22" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="9"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM3_1_PHY.xlsx
+++ b/QCM3_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BA97F2-D993-4CFF-BB0D-89191A17386D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA48E4D-D624-4EE5-BE09-EDBA6C2DDD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
   <si>
     <t>Question</t>
   </si>
@@ -63,9 +63,6 @@
     <t>OptionE</t>
   </si>
   <si>
-    <t>À déterminer</t>
-  </si>
-  <si>
     <t>$C_{AB} = C$</t>
   </si>
   <si>
@@ -90,54 +87,18 @@
     <t>$R_e = \frac{2}{7}R ; C_e = \frac{7}{2}C$</t>
   </si>
   <si>
-    <t>$E_1 = E_2$</t>
-  </si>
-  <si>
-    <t>$E_1 = \frac{C_2}{C_1}E_2$</t>
-  </si>
-  <si>
-    <t>$E_1 = \frac{C_1}{C_2}E_2$</t>
-  </si>
-  <si>
-    <t>$E_1 = (\frac{C_2}{C_1})^2 E_2$</t>
-  </si>
-  <si>
     <t>$u_c = \frac{I_0}{C}t$</t>
   </si>
   <si>
-    <t>$u_c = I_0 t$</t>
-  </si>
-  <si>
     <t>$u_c = I_0 C t$</t>
   </si>
   <si>
     <t>$u_c = C t$</t>
   </si>
   <si>
-    <t>$C = 2,5\text{ \mu F}$</t>
-  </si>
-  <si>
-    <t>$C = 5\text{ \mu F}$</t>
-  </si>
-  <si>
     <t>$C = 0,5\text{ nF}$</t>
   </si>
   <si>
-    <t>$C = 0,5\text{ \mu F}$</t>
-  </si>
-  <si>
-    <t>sur la voie 1 (v1) : $u_C(t)$ ; sur la voie 2 (v2) : $i(t)$</t>
-  </si>
-  <si>
-    <t>sur la voie 1 (v1) : $u_R(t)$ ; sur la voie 2 (v2) : $u_C(t)$</t>
-  </si>
-  <si>
-    <t>sur la voie 1 (v1) : $u_C(t)$ ; sur la voie 2 (v2) : $u(t)$</t>
-  </si>
-  <si>
-    <t>sur la voie 1 (v1) : $u(t)$ ; sur la voie 2 (v2) : $u_C(t)$</t>
-  </si>
-  <si>
     <t>$RC \frac{du_C(t)}{dt} + u_C(t) = 0$</t>
   </si>
   <si>
@@ -231,9 +192,6 @@
     <t>$i(t) = \frac{E}{R} \cdot e^{-t/\tau}$</t>
   </si>
   <si>
-    <t>$i(t) = \frac{E}{RC} \cdot e^{-t/\tau}$</t>
-  </si>
-  <si>
     <t>Courbe 1</t>
   </si>
   <si>
@@ -312,88 +270,155 @@
     <t>La constante de temps $\tau$ vaut environ :</t>
   </si>
   <si>
-    <t>A l'instant $t = \tau$, l'énergie emmagasinée par le condensateur est d'environ :</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Association des condensateurs :&lt;/b&gt;&lt;/center&gt;</t>
   </si>
   <si>
+    <t>L'expression de la charge $Q_{0}$ prise par l'armature A est :</t>
+  </si>
+  <si>
+    <t>À $t = 0$, on bascule K en position 2. &lt;br&gt;&lt;br&gt;
+La charge initiale $q(0)$ de l'armature A est :</t>
+  </si>
+  <si>
+    <t>L'expression de la charge finale $q(\infty)$ du condensateur :</t>
+  </si>
+  <si>
+    <t>L'énergie dissipée par la résistance pendant une durée $\Delta t$ suffisamment petite pour pouvoir considérer $U_R$ constante est :</t>
+  </si>
+  <si>
+    <t>$U_R \cdot I$</t>
+  </si>
+  <si>
+    <t>$\frac{U_R^2}{R} \cdot \Delta t$</t>
+  </si>
+  <si>
+    <t>$R \cdot {I^2}$</t>
+  </si>
+  <si>
+    <t>$U_R \cdot I \cdot \Delta t$</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_3_Q2.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_3_Q3.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_3_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_3_Q5.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_3_Q8.png</t>
+  </si>
+  <si>
+    <t>Le circuit de la figure ci-contre comprend quatre condensateurs dont les capacités sont identiques. &lt;br&gt;&lt;img src="/images/PHY_QCM1_3_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;La capacité $C_{AB}$ du condensateur équivalent est :</t>
+  </si>
+  <si>
+    <t>$E_2 = 0,25 E_1$</t>
+  </si>
+  <si>
+    <t>$E_2 = 1,00 E_1$</t>
+  </si>
+  <si>
+    <t>$E_2 = 3,60 E_1$</t>
+  </si>
+  <si>
+    <t>$E_2 = 2,50 E_1$</t>
+  </si>
+  <si>
+    <t>$E_2 = 4,00 E_1$</t>
+  </si>
+  <si>
+    <t>Les condensateurs du circuit ci-contre sont chargés.
+La tension U_1 aux bornes du condensateur C_1 est :</t>
+  </si>
+  <si>
+    <t>$U_1 = 1 V$</t>
+  </si>
+  <si>
+    <t>$U_1 = 2 V$</t>
+  </si>
+  <si>
+    <t>$U_1 = 4 V$</t>
+  </si>
+  <si>
+    <t>$U_1 = 6 V$</t>
+  </si>
+  <si>
+    <t>$U_1 = 8 V$</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt;Générateur idéal de courant :&lt;/b&gt;&lt;/center&gt;
- On réalise la charge d'un condensateur de capacité $C$, à l'aide d'un générateur idéal de courant qui débite un courant d'intensité constante $I_0 = 0,5\text{ \mu A}$ (Figure 1)</t>
+ On réalise la charge d'un condensateur de capacité $C$, à l'aide d'un générateur idéal de courant qui débite un courant d'intensité constante $I_0 = 0,5 \mu A$ (Figure 1)</t>
+  </si>
+  <si>
+    <t>$u_c = \frac{C}{I_0}t$</t>
+  </si>
+  <si>
+    <t>$C = 2,5 \mu F$</t>
+  </si>
+  <si>
+    <t>$C = 5 \mu F$</t>
+  </si>
+  <si>
+    <t>$C = 0,5 \mu F$</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Un circuit RC : &lt;/b&gt;&lt;/center&gt;
 Un circuit RC est un circuit qui permet de filtrer certaines fréquences d'un signal. C'est un système très utilisé en électronique. On étudie dans cet exercice le circuit suivant. 
-Données : Tension $E=10\text{ V}$ ; Résistance $R = 1\text{ k}\Omega$ ; Constante de temps du circuit $\tau$. 
-A $t = 0\text{ s}$, l'interrupteur K est en position 1. Il bascule en position 2 à $t = t_1$, et revient en position 1 à $t_2$. Le système d'acquisition mesure certaines tensions du circuit en fonction du temps.
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_3_Q6.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Données : 
+&lt;br&gt; * Tension $E=10\text{ V}$ ; 
+&lt;br&gt; * Résistance $R = 1\text{ k}\Omega$ ; 
+&lt;br&gt; * Constante de temps du circuit $\tau$. 
+&lt;br&gt;A $t = 0\text{ s}$, l'interrupteur K est en position 1. Il bascule en position 2 à $t = t_1$, et revient en position 1 à $t_2$. Le système d'acquisition mesure certaines tensions du circuit en fonction du temps.
 On obtient alors les graphiques suivants :</t>
   </si>
   <si>
+    <t>PHY_QCM1_3_Q7.png</t>
+  </si>
+  <si>
+    <t>sur la voie 1 (v1) : $U_C(t)$ ; sur la voie 2 (v2) : $i(t)$</t>
+  </si>
+  <si>
+    <t>sur la voie 1 (v1) : $U_R(t)$ ; sur la voie 2 (v2) : $U_C(t)$</t>
+  </si>
+  <si>
+    <t>sur la voie 1 (v1) : $U_C(t)$ ; sur la voie 2 (v2) : $U(t)$</t>
+  </si>
+  <si>
+    <t>sur la voie 1 (v1) : $U(t)$ ; sur la voie 2 (v2) : $U_C(t)$</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;center&gt;&lt;b&gt;Charge d'un condensateur par deux générateurs : &lt;/b&gt;&lt;/center&gt;
-On étudie la charge q portée par l'armature A du condensateur
-1 - Dans un premier temps, on charge le condensateur sous une tension E (K en position 1 depuis très longtemps)
+&lt;br&gt;On étudie la charge q portée par l'armature A du condensateur
+&lt;br&gt;1 - Dans un premier temps, on charge le condensateur sous une tension E (K en position 1 depuis très longtemps)
 </t>
   </si>
   <si>
-    <t>L'expression de la charge $Q_{0}$ prise par l'armature A est :</t>
-  </si>
-  <si>
-    <t>À $t = 0$, on bascule K en position 2. &lt;br&gt;&lt;br&gt;
-La charge initiale $q(0)$ de l'armature A est :</t>
-  </si>
-  <si>
-    <t>L'expression de la charge finale $q(\infty)$ du condensateur :</t>
+    <t>$i(t) = \frac{-E}{R} \cdot e^{-t/\tau}$</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Dipôle RC : &lt;/b&gt;&lt;/center&gt;
-À $t = 0$, le condensateur est déchargé et on ferme l'interrupteur K. Les courbes ci-dessus représentent l'évolution de la tension $u$ aux bornes du condensateur. La résistance est $R = 1\text{ k}\Omega$.</t>
-  </si>
-  <si>
-    <t>L'énergie dissipée par la résistance pendant une durée $\Delta t$ suffisamment petite pour pouvoir considérer $U_R$ constante est :</t>
-  </si>
-  <si>
-    <t>$U_R \cdot I$</t>
-  </si>
-  <si>
-    <t>$\frac{U_R^2}{R} \cdot \Delta t$</t>
-  </si>
-  <si>
-    <t>$R \cdot {I^2}$</t>
-  </si>
-  <si>
-    <t>$U_R \cdot I \cdot \Delta t$</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q2.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q3.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q4.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q5.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q6.png; PHY_QCM1_3_Q7.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q8.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_3_Q9.png; PHY_QCM1_3_Q10.png</t>
-  </si>
-  <si>
-    <t>Le circuit de la figure ci-contre comprend quatre condensateurs dont les capacités sont identiques. &lt;br&gt;&lt;img src="/images/PHY_QCM1_3_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;La capacité $C_{AB}$ du condensateur équivalent est :</t>
+&lt;br&gt;À $t = 0$, le condensateur est déchargé et on ferme l'interrupteur K. 
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_3_Q9.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Les courbes ci-dessus représentent l'évolution de la tension $u$ aux bornes du condensateur. La résistance est $R = 1\text{ k}\Omega$.</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_3_Q10.png</t>
+  </si>
+  <si>
+    <t>A l'instant $t = 5 ms$, l'énergie emmagasinée par le condensateur est d'environ :</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,12 +439,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -531,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -567,23 +586,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -890,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -938,29 +954,29 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>16</v>
       </c>
       <c r="H2" s="14"/>
       <c r="I2" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="6"/>
@@ -968,202 +984,205 @@
     <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="10" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="G6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="H6" s="14"/>
+      <c r="I6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="G7" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="19" t="s">
+      <c r="B8" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -1171,26 +1190,26 @@
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="10" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -1198,138 +1217,138 @@
     <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="10" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="14" t="s">
-        <v>104</v>
+      <c r="B12" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>108</v>
+        <v>36</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="14" t="s">
-        <v>106</v>
+      <c r="I12" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="102" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>99</v>
-      </c>
+    <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
       <c r="B13" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>53</v>
+        <v>85</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="14"/>
+        <v>89</v>
+      </c>
+      <c r="H13" s="10"/>
       <c r="I13" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>114</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+    <row r="14" spans="1:11" ht="102" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="B14" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="10" t="s">
-        <v>102</v>
+      <c r="A15" s="13"/>
+      <c r="B15" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -1337,181 +1356,208 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="10" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="10" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="10" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="H22" s="10"/>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="11"/>
+      <c r="B23" s="9"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
